--- a/exports/trend_1d/AXISBANK_full_report.xlsx
+++ b/exports/trend_1d/AXISBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.24</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42081</v>
+        <v>42082</v>
       </c>
       <c r="H2" t="n">
-        <v>581.25</v>
+        <v>563.54</v>
       </c>
       <c r="I2" t="n">
         <v>566.4229515921724</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K2" t="n">
-        <v>13.07</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>0.57</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.15</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H3" t="n">
-        <v>574.65</v>
+        <v>585.4</v>
       </c>
       <c r="I3" t="n">
         <v>579.9008654491306</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.97</v>
+        <v>-3.88</v>
       </c>
       <c r="L3" t="n">
         <v>5.68</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.41</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42209</v>
+        <v>42212</v>
       </c>
       <c r="H4" t="n">
-        <v>580.45</v>
+        <v>555.79</v>
       </c>
       <c r="I4" t="n">
         <v>563.9241481353479</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.85</v>
+        <v>-5.06</v>
       </c>
       <c r="L4" t="n">
         <v>8</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.53</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42265</v>
+        <v>42268</v>
       </c>
       <c r="H5" t="n">
-        <v>517.45</v>
+        <v>528</v>
       </c>
       <c r="I5" t="n">
         <v>523.5347372793151</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K5" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>6.07</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>13.26</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42304</v>
+        <v>42305</v>
       </c>
       <c r="H6" t="n">
-        <v>521.79</v>
+        <v>482.9</v>
       </c>
       <c r="I6" t="n">
         <v>485.7898351555368</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.18</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>8.300000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="M6" t="n">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>3.47</v>
+        <v>7.45</v>
       </c>
       <c r="O6" t="n">
         <v>2.04</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.93</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42390</v>
+        <v>42391</v>
       </c>
       <c r="H7" t="n">
-        <v>409.15</v>
+        <v>424.15</v>
       </c>
       <c r="I7" t="n">
         <v>418.7774707140961</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K7" t="n">
-        <v>15.27</v>
+        <v>12.17</v>
       </c>
       <c r="L7" t="n">
         <v>2.65</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.62</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42635</v>
+        <v>42636</v>
       </c>
       <c r="H8" t="n">
-        <v>591.8</v>
+        <v>557.45</v>
       </c>
       <c r="I8" t="n">
         <v>586.8539305402094</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K8" t="n">
-        <v>39.53</v>
+        <v>31.43</v>
       </c>
       <c r="L8" t="n">
         <v>11.99</v>
@@ -897,7 +992,7 @@
         <v>4.64</v>
       </c>
       <c r="N8" t="n">
-        <v>4.17</v>
+        <v>5.8</v>
       </c>
       <c r="O8" t="n">
         <v>3.67</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.06</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42747</v>
+        <v>42748</v>
       </c>
       <c r="H9" t="n">
-        <v>455.2</v>
+        <v>472.8</v>
       </c>
       <c r="I9" t="n">
         <v>467.8783729955356</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K9" t="n">
-        <v>18.34</v>
+        <v>15.19</v>
       </c>
       <c r="L9" t="n">
         <v>6.93</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>9.66</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42754</v>
+        <v>42755</v>
       </c>
       <c r="H10" t="n">
-        <v>483.8</v>
+        <v>450.75</v>
       </c>
       <c r="I10" t="n">
         <v>451.1676898973477</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>2.33</v>
+        <v>-4.66</v>
       </c>
       <c r="L10" t="n">
-        <v>3.72</v>
+        <v>5.25</v>
       </c>
       <c r="M10" t="n">
-        <v>0.37</v>
+        <v>5.33</v>
       </c>
       <c r="N10" t="n">
-        <v>0.96</v>
+        <v>6.83</v>
       </c>
       <c r="O10" t="n">
         <v>3.87</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.33</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42768</v>
+        <v>42769</v>
       </c>
       <c r="H11" t="n">
-        <v>482.55</v>
+        <v>490.7</v>
       </c>
       <c r="I11" t="n">
         <v>486.2896290648335</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.05</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>7.82</v>
+        <v>9.26</v>
       </c>
       <c r="M11" t="n">
         <v>0.63</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.75</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42954</v>
+        <v>42955</v>
       </c>
       <c r="H12" t="n">
-        <v>505.8</v>
+        <v>499.45</v>
       </c>
       <c r="I12" t="n">
         <v>504.4812903155206</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K12" t="n">
-        <v>3.08</v>
+        <v>1.78</v>
       </c>
       <c r="L12" t="n">
         <v>2.25</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.86</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42993</v>
+        <v>42996</v>
       </c>
       <c r="H13" t="n">
-        <v>516.15</v>
+        <v>524.55</v>
       </c>
       <c r="I13" t="n">
         <v>520.5119875331811</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.34</v>
+        <v>-5.03</v>
       </c>
       <c r="L13" t="n">
-        <v>4.47</v>
+        <v>5.32</v>
       </c>
       <c r="M13" t="n">
         <v>1.16</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>6.17</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43025</v>
+        <v>43026</v>
       </c>
       <c r="H14" t="n">
-        <v>513.15</v>
+        <v>464.5</v>
       </c>
       <c r="I14" t="n">
         <v>495.1506995467885</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.17</v>
+        <v>-11.45</v>
       </c>
       <c r="L14" t="n">
-        <v>6.91</v>
+        <v>12.13</v>
       </c>
       <c r="M14" t="n">
-        <v>0.77</v>
+        <v>4.9</v>
       </c>
       <c r="N14" t="n">
-        <v>1.72</v>
+        <v>9.48</v>
       </c>
       <c r="O14" t="n">
         <v>1.63</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>12.67</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43038</v>
+        <v>43039</v>
       </c>
       <c r="H15" t="n">
-        <v>484</v>
+        <v>523.15</v>
       </c>
       <c r="I15" t="n">
         <v>500.0852016746169</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.2</v>
+        <v>-12.63</v>
       </c>
       <c r="L15" t="n">
-        <v>5.79</v>
+        <v>13.89</v>
       </c>
       <c r="M15" t="n">
         <v>3.58</v>
       </c>
       <c r="N15" t="n">
-        <v>4.66</v>
+        <v>8.09</v>
       </c>
       <c r="O15" t="n">
         <v>-9.48</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>12.52</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H16" t="n">
-        <v>592.8</v>
+        <v>564.9</v>
       </c>
       <c r="I16" t="n">
         <v>573.8038176590758</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="n">
-        <v>13.31</v>
+        <v>7.98</v>
       </c>
       <c r="L16" t="n">
         <v>5.71</v>
@@ -1353,7 +1544,7 @@
         <v>1.82</v>
       </c>
       <c r="N16" t="n">
-        <v>2.57</v>
+        <v>4.71</v>
       </c>
       <c r="O16" t="n">
         <v>8.09</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.04</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43199</v>
+        <v>43200</v>
       </c>
       <c r="H17" t="n">
-        <v>519.3</v>
+        <v>546.15</v>
       </c>
       <c r="I17" t="n">
         <v>540.3259298296666</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K17" t="n">
-        <v>8.07</v>
+        <v>3.32</v>
       </c>
       <c r="L17" t="n">
         <v>4.05</v>
@@ -1410,7 +1613,7 @@
         <v>1.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.82</v>
+        <v>5.17</v>
       </c>
       <c r="O17" t="n">
         <v>-4.71</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>10.81</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43215</v>
+        <v>43216</v>
       </c>
       <c r="H18" t="n">
-        <v>498.4</v>
+        <v>493.75</v>
       </c>
       <c r="I18" t="n">
         <v>496.1908644448801</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" t="n">
-        <v>-8.74</v>
+        <v>-9.59</v>
       </c>
       <c r="L18" t="n">
-        <v>9.130000000000001</v>
+        <v>11.51</v>
       </c>
       <c r="M18" t="n">
         <v>0.46</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.5</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43216</v>
+        <v>43217</v>
       </c>
       <c r="H19" t="n">
-        <v>493.75</v>
+        <v>539.2</v>
       </c>
       <c r="I19" t="n">
         <v>535.6989316536318</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>9.99</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>-0.93</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>15.72</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43277</v>
+        <v>43278</v>
       </c>
       <c r="H20" t="n">
-        <v>514.2</v>
+        <v>507.85</v>
       </c>
       <c r="I20" t="n">
         <v>508.077907021425</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.64</v>
+        <v>-5.81</v>
       </c>
       <c r="L20" t="n">
         <v>10.75</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>7.36</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H21" t="n">
-        <v>540.35</v>
+        <v>546.1</v>
       </c>
       <c r="I21" t="n">
         <v>543.7500143878856</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.4</v>
+        <v>-7.53</v>
       </c>
       <c r="L21" t="n">
-        <v>7.45</v>
+        <v>8.08</v>
       </c>
       <c r="M21" t="n">
         <v>0.61</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.35</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43360</v>
+        <v>43361</v>
       </c>
       <c r="H22" t="n">
-        <v>625.95</v>
+        <v>608.6</v>
       </c>
       <c r="I22" t="n">
         <v>610.3578746176703</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K22" t="n">
-        <v>14.62</v>
+        <v>11.44</v>
       </c>
       <c r="L22" t="n">
         <v>3.61</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>11.69</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43406</v>
+        <v>43409</v>
       </c>
       <c r="H23" t="n">
-        <v>610.65</v>
+        <v>624.4</v>
       </c>
       <c r="I23" t="n">
         <v>619.2879168409372</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.34</v>
+        <v>-2.6</v>
       </c>
       <c r="L23" t="n">
         <v>4.17</v>
       </c>
       <c r="M23" t="n">
-        <v>2.09</v>
+        <v>2.99</v>
       </c>
       <c r="N23" t="n">
         <v>6.58</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.11</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43599</v>
+        <v>43600</v>
       </c>
       <c r="H24" t="n">
-        <v>731.35</v>
+        <v>721.95</v>
       </c>
       <c r="I24" t="n">
         <v>730.4777019841097</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K24" t="n">
-        <v>17.13</v>
+        <v>15.62</v>
       </c>
       <c r="L24" t="n">
         <v>7.03</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>6.92</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H25" t="n">
-        <v>748.95</v>
+        <v>782.4</v>
       </c>
       <c r="I25" t="n">
         <v>771.9362541410298</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.74</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>4.18</v>
+        <v>9.52</v>
       </c>
       <c r="M25" t="n">
-        <v>0.61</v>
+        <v>1.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.34</v>
+        <v>4.47</v>
       </c>
       <c r="O25" t="n">
         <v>-1.29</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43637</v>
+        <v>43640</v>
       </c>
       <c r="H26" t="n">
-        <v>771.05</v>
+        <v>762.85</v>
       </c>
       <c r="I26" t="n">
         <v>768.7405672809581</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.45</v>
+        <v>-2.5</v>
       </c>
       <c r="L26" t="n">
         <v>3.01</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>7.62</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H27" t="n">
-        <v>680.35</v>
+        <v>725.5</v>
       </c>
       <c r="I27" t="n">
         <v>697.4450039675875</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K27" t="n">
-        <v>10.81</v>
+        <v>4.9</v>
       </c>
       <c r="L27" t="n">
         <v>7.36</v>
       </c>
       <c r="M27" t="n">
-        <v>2.01</v>
+        <v>3.46</v>
       </c>
       <c r="N27" t="n">
-        <v>6.6</v>
+        <v>6.64</v>
       </c>
       <c r="O27" t="n">
         <v>-1.06</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.49</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43851</v>
+        <v>43852</v>
       </c>
       <c r="H28" t="n">
-        <v>717.6</v>
+        <v>712.6</v>
       </c>
       <c r="I28" t="n">
         <v>714.426441017063</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.09</v>
+        <v>-1.78</v>
       </c>
       <c r="L28" t="n">
         <v>10.86</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>6.78</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43872</v>
+        <v>43873</v>
       </c>
       <c r="H29" t="n">
-        <v>749.95</v>
+        <v>755.25</v>
       </c>
       <c r="I29" t="n">
         <v>754.3748301865656</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.24</v>
+        <v>-5.99</v>
       </c>
       <c r="L29" t="n">
-        <v>6.24</v>
+        <v>6.75</v>
       </c>
       <c r="M29" t="n">
         <v>1.75</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>5.9</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H30" t="n">
-        <v>735.85</v>
+        <v>697.3</v>
       </c>
       <c r="I30" t="n">
         <v>710.6726249962393</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.57</v>
+        <v>-7.67</v>
       </c>
       <c r="L30" t="n">
-        <v>5.12</v>
+        <v>8.51</v>
       </c>
       <c r="M30" t="n">
-        <v>0.85</v>
+        <v>2.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.53</v>
+        <v>5.24</v>
       </c>
       <c r="O30" t="n">
         <v>0.71</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.49</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43987</v>
+        <v>43990</v>
       </c>
       <c r="H31" t="n">
-        <v>405.3</v>
+        <v>430.25</v>
       </c>
       <c r="I31" t="n">
         <v>414.5681118794364</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K31" t="n">
-        <v>41.88</v>
+        <v>38.3</v>
       </c>
       <c r="L31" t="n">
         <v>3.93</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>18.21</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H32" t="n">
-        <v>458.7</v>
+        <v>444.35</v>
       </c>
       <c r="I32" t="n">
         <v>452.4184858633098</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K32" t="n">
-        <v>6.61</v>
+        <v>3.28</v>
       </c>
       <c r="L32" t="n">
         <v>16.23</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>14.71</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44112</v>
+        <v>44113</v>
       </c>
       <c r="H33" t="n">
-        <v>451.9</v>
+        <v>468.05</v>
       </c>
       <c r="I33" t="n">
         <v>459.3915738448425</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.7</v>
+        <v>-5.33</v>
       </c>
       <c r="L33" t="n">
-        <v>4.06</v>
+        <v>5.73</v>
       </c>
       <c r="M33" t="n">
         <v>1.48</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>12.29</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H34" t="n">
-        <v>706.4</v>
+        <v>694.6</v>
       </c>
       <c r="I34" t="n">
         <v>694.610718824361</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K34" t="n">
-        <v>50.92</v>
+        <v>48.4</v>
       </c>
       <c r="L34" t="n">
         <v>3.82</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>11.61</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44314</v>
+        <v>44315</v>
       </c>
       <c r="H35" t="n">
-        <v>708.15</v>
+        <v>719.4</v>
       </c>
       <c r="I35" t="n">
         <v>714.9092706775243</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.95</v>
+        <v>-3.57</v>
       </c>
       <c r="L35" t="n">
-        <v>3.22</v>
+        <v>4.65</v>
       </c>
       <c r="M35" t="n">
         <v>3.37</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.58</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44403</v>
+        <v>44404</v>
       </c>
       <c r="H36" t="n">
-        <v>756.3</v>
+        <v>731.7</v>
       </c>
       <c r="I36" t="n">
         <v>731.9477821459838</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K36" t="n">
-        <v>5.13</v>
+        <v>1.71</v>
       </c>
       <c r="L36" t="n">
         <v>5.28</v>
@@ -2493,7 +2924,7 @@
         <v>2.44</v>
       </c>
       <c r="N36" t="n">
-        <v>2.27</v>
+        <v>3.25</v>
       </c>
       <c r="O36" t="n">
         <v>1.59</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H37" t="n">
-        <v>755.5</v>
+        <v>761.55</v>
       </c>
       <c r="I37" t="n">
         <v>760.7635888046624</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.25</v>
+        <v>-4.08</v>
       </c>
       <c r="L37" t="n">
-        <v>3.55</v>
+        <v>4.41</v>
       </c>
       <c r="M37" t="n">
         <v>0.86</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.51</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H38" t="n">
-        <v>787.5</v>
+        <v>758.35</v>
       </c>
       <c r="I38" t="n">
         <v>782.6375232255243</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K38" t="n">
-        <v>3.41</v>
+        <v>-0.42</v>
       </c>
       <c r="L38" t="n">
         <v>3.95</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.15</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44544</v>
+        <v>44545</v>
       </c>
       <c r="H39" t="n">
-        <v>710.9</v>
+        <v>712.5</v>
       </c>
       <c r="I39" t="n">
         <v>711.1621602997216</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K39" t="n">
-        <v>6.26</v>
+        <v>6.05</v>
       </c>
       <c r="L39" t="n">
         <v>4.04</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.16</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H40" t="n">
-        <v>777.2</v>
+        <v>730.3</v>
       </c>
       <c r="I40" t="n">
         <v>750.7580782907939</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K40" t="n">
-        <v>9.08</v>
+        <v>2.5</v>
       </c>
       <c r="L40" t="n">
         <v>7.94</v>
       </c>
       <c r="M40" t="n">
-        <v>2.88</v>
+        <v>3.19</v>
       </c>
       <c r="N40" t="n">
-        <v>3.79</v>
+        <v>6.03</v>
       </c>
       <c r="O40" t="n">
         <v>0.23</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.83</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44649</v>
+        <v>44650</v>
       </c>
       <c r="H41" t="n">
-        <v>737.8</v>
+        <v>750.45</v>
       </c>
       <c r="I41" t="n">
         <v>743.8690628021494</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.03</v>
+        <v>-2.76</v>
       </c>
       <c r="L41" t="n">
         <v>5.32</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44679</v>
+        <v>44680</v>
       </c>
       <c r="H42" t="n">
-        <v>779.8</v>
+        <v>728.6</v>
       </c>
       <c r="I42" t="n">
         <v>740.7489843995673</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
-        <v>3.91</v>
+        <v>-2.91</v>
       </c>
       <c r="L42" t="n">
-        <v>1.22</v>
+        <v>3.39</v>
       </c>
       <c r="M42" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="N42" t="n">
-        <v>2.64</v>
+        <v>6.57</v>
       </c>
       <c r="O42" t="n">
         <v>1.71</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.65</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44750</v>
+        <v>44753</v>
       </c>
       <c r="H43" t="n">
-        <v>669.15</v>
+        <v>679.85</v>
       </c>
       <c r="I43" t="n">
         <v>676.5780383016283</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K43" t="n">
-        <v>8.16</v>
+        <v>6.69</v>
       </c>
       <c r="L43" t="n">
         <v>5.25</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.73</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H44" t="n">
-        <v>768.6</v>
+        <v>742.6</v>
       </c>
       <c r="I44" t="n">
         <v>761.5921426718762</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K44" t="n">
-        <v>13.05</v>
+        <v>9.23</v>
       </c>
       <c r="L44" t="n">
         <v>3.05</v>
@@ -2949,7 +3476,7 @@
         <v>2.4</v>
       </c>
       <c r="N44" t="n">
-        <v>2.87</v>
+        <v>3.38</v>
       </c>
       <c r="O44" t="n">
         <v>1.6</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.84</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44844</v>
+        <v>44845</v>
       </c>
       <c r="H45" t="n">
-        <v>776.85</v>
+        <v>785.55</v>
       </c>
       <c r="I45" t="n">
         <v>781.4732817813153</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.61</v>
+        <v>-5.78</v>
       </c>
       <c r="L45" t="n">
-        <v>4.86</v>
+        <v>7.12</v>
       </c>
       <c r="M45" t="n">
         <v>1.47</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.17</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44950</v>
+        <v>44951</v>
       </c>
       <c r="H46" t="n">
-        <v>910.2</v>
+        <v>892.35</v>
       </c>
       <c r="I46" t="n">
         <v>908.6886821530487</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K46" t="n">
-        <v>15.87</v>
+        <v>13.6</v>
       </c>
       <c r="L46" t="n">
         <v>1.41</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.89</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45037</v>
+        <v>45040</v>
       </c>
       <c r="H47" t="n">
-        <v>864.2</v>
+        <v>882.3</v>
       </c>
       <c r="I47" t="n">
         <v>880.2074168764523</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K47" t="n">
-        <v>3.15</v>
+        <v>1.13</v>
       </c>
       <c r="L47" t="n">
         <v>1.69</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.57</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45140</v>
+        <v>45141</v>
       </c>
       <c r="H48" t="n">
-        <v>945.25</v>
+        <v>935.55</v>
       </c>
       <c r="I48" t="n">
         <v>939.7157583943241</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K48" t="n">
-        <v>7.13</v>
+        <v>6.04</v>
       </c>
       <c r="L48" t="n">
         <v>3.25</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.35</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45162</v>
+        <v>45163</v>
       </c>
       <c r="H49" t="n">
-        <v>981.35</v>
+        <v>983.1</v>
       </c>
       <c r="I49" t="n">
         <v>982.5736690274645</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.9</v>
+        <v>-5.08</v>
       </c>
       <c r="L49" t="n">
         <v>6.27</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.08</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45218</v>
+        <v>45219</v>
       </c>
       <c r="H50" t="n">
-        <v>991.4</v>
+        <v>980.35</v>
       </c>
       <c r="I50" t="n">
         <v>986.8790593629864</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K50" t="n">
-        <v>0.84</v>
+        <v>-0.28</v>
       </c>
       <c r="L50" t="n">
         <v>2.17</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>6.18</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H51" t="n">
-        <v>1020.9</v>
+        <v>1021.7</v>
       </c>
       <c r="I51" t="n">
         <v>1020.924418277049</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.14</v>
+        <v>-4.22</v>
       </c>
       <c r="L51" t="n">
-        <v>4.27</v>
+        <v>4.75</v>
       </c>
       <c r="M51" t="n">
         <v>0.89</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>5.54</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45247</v>
+        <v>45250</v>
       </c>
       <c r="H52" t="n">
-        <v>994.35</v>
+        <v>988.7</v>
       </c>
       <c r="I52" t="n">
         <v>989.5519518199479</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.68</v>
+        <v>-3.23</v>
       </c>
       <c r="L52" t="n">
-        <v>2.92</v>
+        <v>4.05</v>
       </c>
       <c r="M52" t="n">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="N52" t="n">
         <v>3.12</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.39</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="H53" t="n">
-        <v>1021.15</v>
+        <v>1060.15</v>
       </c>
       <c r="I53" t="n">
         <v>1042.013652123258</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.28</v>
+        <v>-7.23</v>
       </c>
       <c r="L53" t="n">
-        <v>3.36</v>
+        <v>7.57</v>
       </c>
       <c r="M53" t="n">
-        <v>0.45</v>
+        <v>0.59</v>
       </c>
       <c r="N53" t="n">
-        <v>1.25</v>
+        <v>3.82</v>
       </c>
       <c r="O53" t="n">
         <v>-0.57</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>6.79</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45314</v>
+        <v>45315</v>
       </c>
       <c r="H54" t="n">
-        <v>1089.25</v>
+        <v>1059.15</v>
       </c>
       <c r="I54" t="n">
         <v>1073.037913984118</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K54" t="n">
-        <v>2.74</v>
+        <v>-0.09</v>
       </c>
       <c r="L54" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="M54" t="n">
-        <v>3.32</v>
+        <v>5</v>
       </c>
       <c r="N54" t="n">
         <v>3.29</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>7.83</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45406</v>
+        <v>45407</v>
       </c>
       <c r="H55" t="n">
-        <v>1063.25</v>
+        <v>1127</v>
       </c>
       <c r="I55" t="n">
         <v>1085.71519124825</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.39</v>
+        <v>-6.41</v>
       </c>
       <c r="L55" t="n">
-        <v>6.87</v>
+        <v>7.06</v>
       </c>
       <c r="M55" t="n">
-        <v>1.3</v>
+        <v>3.46</v>
       </c>
       <c r="N55" t="n">
-        <v>2.44</v>
+        <v>6</v>
       </c>
       <c r="O55" t="n">
         <v>-2.76</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>8.56</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45497</v>
+        <v>45498</v>
       </c>
       <c r="H56" t="n">
-        <v>1239.25</v>
+        <v>1175.9</v>
       </c>
       <c r="I56" t="n">
         <v>1232.161499453931</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K56" t="n">
-        <v>9.960000000000001</v>
+        <v>4.34</v>
       </c>
       <c r="L56" t="n">
         <v>3.63</v>
       </c>
       <c r="M56" t="n">
-        <v>0.96</v>
+        <v>3.17</v>
       </c>
       <c r="N56" t="n">
         <v>7.57</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.65</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45547</v>
+        <v>45548</v>
       </c>
       <c r="H57" t="n">
-        <v>1203.35</v>
+        <v>1217.45</v>
       </c>
       <c r="I57" t="n">
         <v>1211.868559627201</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.33</v>
+        <v>-3.53</v>
       </c>
       <c r="L57" t="n">
-        <v>2.53</v>
+        <v>3.71</v>
       </c>
       <c r="M57" t="n">
         <v>1.22</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.51</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H58" t="n">
-        <v>1226.65</v>
+        <v>1175.7</v>
       </c>
       <c r="I58" t="n">
         <v>1210.351021199643</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>0.76</v>
+        <v>-3.43</v>
       </c>
       <c r="L58" t="n">
-        <v>1.35</v>
+        <v>3.64</v>
       </c>
       <c r="M58" t="n">
-        <v>0.76</v>
+        <v>1.56</v>
       </c>
       <c r="N58" t="n">
-        <v>3.22</v>
+        <v>4.15</v>
       </c>
       <c r="O58" t="n">
         <v>1.17</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45691</v>
+        <v>45692</v>
       </c>
       <c r="H59" t="n">
-        <v>989.4</v>
+        <v>1015.3</v>
       </c>
       <c r="I59" t="n">
         <v>1013.063093441664</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K59" t="n">
-        <v>15.85</v>
+        <v>13.64</v>
       </c>
       <c r="L59" t="n">
         <v>3.7</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.99</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
       <c r="H60" t="n">
-        <v>1175.1</v>
+        <v>1165.4</v>
       </c>
       <c r="I60" t="n">
         <v>1170.066295481234</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K60" t="n">
-        <v>15.74</v>
+        <v>14.78</v>
       </c>
       <c r="L60" t="n">
         <v>3.67</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>6</v>
+      </c>
+      <c r="U60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.68</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="H61" t="n">
-        <v>1087.4</v>
+        <v>1105.3</v>
       </c>
       <c r="I61" t="n">
         <v>1097.146624671979</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K61" t="n">
-        <v>6.69</v>
+        <v>5.16</v>
       </c>
       <c r="L61" t="n">
         <v>1.25</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.11</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="H62" t="n">
-        <v>1284.8</v>
+        <v>1219.6</v>
       </c>
       <c r="I62" t="n">
         <v>1232.682078042423</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K62" t="n">
-        <v>16.24</v>
+        <v>10.34</v>
       </c>
       <c r="L62" t="n">
         <v>1.53</v>
@@ -3975,7 +4718,7 @@
         <v>0.8</v>
       </c>
       <c r="N62" t="n">
-        <v>2.14</v>
+        <v>5.07</v>
       </c>
       <c r="O62" t="n">
         <v>1.65</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>7.81</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="H63" t="n">
-        <v>1266.9</v>
+        <v>1285.8</v>
       </c>
       <c r="I63" t="n">
         <v>1277.613523711768</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.88</v>
+        <v>-5.43</v>
       </c>
       <c r="L63" t="n">
-        <v>5.1</v>
+        <v>5.75</v>
       </c>
       <c r="M63" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="N63" t="n">
         <v>1.88</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>4.76</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="H64" t="n">
-        <v>1349.1</v>
+        <v>1315.8</v>
       </c>
       <c r="I64" t="n">
         <v>1315.83159803868</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K64" t="n">
-        <v>4.92</v>
+        <v>2.33</v>
       </c>
       <c r="L64" t="n">
         <v>2.94</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>7.53</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H65" t="n">
-        <v>1250.1</v>
+        <v>1333</v>
       </c>
       <c r="I65" t="n">
         <v>1280.539573946083</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K65" t="n">
-        <v>4.99</v>
+        <v>-1.31</v>
       </c>
       <c r="L65" t="n">
         <v>2.44</v>
       </c>
       <c r="M65" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="N65" t="n">
-        <v>3.96</v>
+        <v>6.63</v>
       </c>
       <c r="O65" t="n">
         <v>-2.47</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>11.11</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="H66" t="n">
-        <v>1296.4</v>
+        <v>1268.3</v>
       </c>
       <c r="I66" t="n">
         <v>1275.109758576494</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.75</v>
+        <v>-4.85</v>
       </c>
       <c r="L66" t="n">
-        <v>4.05</v>
+        <v>5.68</v>
       </c>
       <c r="M66" t="n">
         <v>2.99</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>8.82</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H67" t="n">
-        <v>1317.3</v>
+        <v>1356.3</v>
       </c>
       <c r="I67" t="n">
         <v>1321.50045428993</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.86</v>
+        <v>-6.94</v>
       </c>
       <c r="L67" t="n">
-        <v>5.61</v>
+        <v>7.11</v>
       </c>
       <c r="M67" t="n">
         <v>1.21</v>
       </c>
       <c r="N67" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="O67" t="n">
         <v>-2.17</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>7.93</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="H68" t="n">
-        <v>1341</v>
+        <v>1309.5</v>
       </c>
       <c r="I68" t="n">
         <v>1314.273195864467</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.13</v>
+        <v>-3.45</v>
       </c>
       <c r="L68" t="n">
-        <v>2.79</v>
+        <v>3.86</v>
       </c>
       <c r="M68" t="n">
         <v>0.55</v>
       </c>
       <c r="N68" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="O68" t="n">
         <v>2.96</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>7.58</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="H69" t="n">
-        <v>1265</v>
+        <v>1300</v>
       </c>
       <c r="I69" t="n">
         <v>1274.80715742002</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K69" t="n">
-        <v>3.4</v>
+        <v>0.73</v>
       </c>
       <c r="L69" t="n">
         <v>2.94</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>6.96</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H70" t="n">
-        <v>1243.2</v>
+        <v>1186.5</v>
       </c>
       <c r="I70" t="n">
         <v>1209.492932867841</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.37</v>
+        <v>-8.73</v>
       </c>
       <c r="L70" t="n">
-        <v>6.16</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M70" t="n">
         <v>1.93</v>
       </c>
       <c r="N70" t="n">
-        <v>3.23</v>
+        <v>4.56</v>
       </c>
       <c r="O70" t="n">
         <v>2.77</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>7.62</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H71" t="n">
-        <v>1264.6</v>
+        <v>1288</v>
       </c>
       <c r="I71" t="n">
         <v>1276.918490557086</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.58</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>7.55</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M71" t="n">
         <v>0.98</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4548,6 +5411,14 @@
       <c r="Q72" t="n">
         <v>9</v>
       </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9506,7 +10377,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.9</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="6">
@@ -9516,7 +10387,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -9526,7 +10397,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8">
@@ -9536,7 +10407,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -9546,7 +10417,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87.5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -9556,7 +10427,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111.9</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="11">
@@ -9566,7 +10437,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -9576,7 +10447,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -9586,7 +10457,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.3</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="14">
@@ -9596,7 +10467,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.45</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="15">
@@ -9606,7 +10477,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.74</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="16">
@@ -9616,7 +10487,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.16</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="17">
@@ -9626,7 +10497,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50.92</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="18">
@@ -9636,7 +10507,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.4</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="19">
@@ -9646,7 +10517,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.86</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="20">
@@ -9656,7 +10527,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.06</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="21">
@@ -9676,7 +10547,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -9686,7 +10557,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -9696,7 +10567,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="25">
@@ -9716,7 +10587,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.69</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="27">
@@ -9736,7 +10607,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
